--- a/docs/qa/upload-templates/work_centre_master_upload_template.xlsx
+++ b/docs/qa/upload-templates/work_centre_master_upload_template.xlsx
@@ -133,12 +133,22 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Required</t>
+        <t>Required WC code</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Required</t>
+        <t>Available hours/day (required)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Plant / bay (required)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>0-100</t>
       </text>
     </comment>
   </commentList>
@@ -434,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +460,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>name_ar</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>capacity_hrs_day</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>shifts_per_day</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>efficiency_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>calendar_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cost_per_hour</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -465,8 +510,37 @@
           <t>Winding</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>اللف</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>16</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bay-A</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CAL-STD</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -480,8 +554,37 @@
           <t>Assembly</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>التجميع</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bay-B</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CAL-STD</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -492,11 +595,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>Testing &amp; QC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>الاختبار</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lab-1</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>95</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CAL-STD</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
